--- a/workshop_prep/item2_fullprice_recovery_backup.xlsx
+++ b/workshop_prep/item2_fullprice_recovery_backup.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="3.1 Channel Margin Level" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3.2 ASP Trend by Channel" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3.2-6 Mix vs Rate Decomp" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4 Ecom Monthly Discount" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4 Ecom Erosion Months" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5.1 Wholesale by Account" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5.2 Wholesale by Ordertype" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5.3 Wholesale by Layer" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6 Retail by Layer" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7 Consolidated Sizing" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8 FW27 Style Detail" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="8 FW27 by Layer" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="8 FW27 by CarryOver" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.1 Channel Margin Level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 ASP Trend by Channel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2-6 Mix vs Rate Decomp" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Ecom Monthly Discount" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Ecom Erosion Months" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1 Wholesale by Account" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.2 Wholesale by Ordertype" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.3 Wholesale by Layer" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Retail by Layer" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Consolidated Sizing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 FW27 Style Detail" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 FW27 by Layer" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 FW27 by CarryOver" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Channel Margin" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Same-Franchise ASP-COGS" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,7 +694,6 @@
       <c r="B5" t="n">
         <v>16034325</v>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8472,6 +8473,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FY2025_GM%_core</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>YTD2026_GM%_core</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>49</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>N_continuing_franchises</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ASP_FY2025</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ASP_YTD2026</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ASP_chg_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>COGSu_FY2025</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>COGSu_YTD2026</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>COGSu_chg_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GM_FY2025_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GM_YTD2026_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2" t="n">
+        <v>824</v>
+      </c>
+      <c r="D2" t="n">
+        <v>811.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wholesale (core, excl. closeout)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C3" t="n">
+        <v>616.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>541.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>332</v>
+      </c>
+      <c r="G3" t="n">
+        <v>278.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
